--- a/Luban/DataTables/Datas/Item.xlsx
+++ b/Luban/DataTables/Datas/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26880" windowHeight="9285"/>
+    <workbookView windowWidth="30705" windowHeight="9885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -77,9 +77,27 @@
     <t>icon</t>
   </si>
   <si>
+    <t>desc</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
+    <t>bagType</t>
+  </si>
+  <si>
+    <t>maxCount</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>exdata</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -89,10 +107,13 @@
     <t>string</t>
   </si>
   <si>
-    <t>int#ref=Common.TextRecord</t>
-  </si>
-  <si>
-    <t>int#ref=Res.IconRecord</t>
+    <t>int#ref=Common.Dictionary</t>
+  </si>
+  <si>
+    <t>int#ref=Res.Icon</t>
+  </si>
+  <si>
+    <t>(list#sep=;),int</t>
   </si>
   <si>
     <t>##group</t>
@@ -101,16 +122,37 @@
     <t>c</t>
   </si>
   <si>
+    <t>c,s</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
+    <t>物品名</t>
+  </si>
+  <si>
     <t>图标表ID</t>
   </si>
   <si>
+    <t>描述</t>
+  </si>
+  <si>
     <t>物品类型</t>
+  </si>
+  <si>
+    <t>包裹类型</t>
+  </si>
+  <si>
+    <t>最大数量</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>获取途径</t>
   </si>
   <si>
     <t>等级</t>
@@ -767,18 +809,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1099,18 +1150,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:Y14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" style="3" customWidth="1"/>
     <col min="3" max="3" width="15.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="12.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="32.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.375" style="3" customWidth="1"/>
-    <col min="7" max="10" width="18" customWidth="1"/>
+    <col min="5" max="6" width="32.375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.375" style="3" customWidth="1"/>
+    <col min="8" max="11" width="18" style="3" customWidth="1"/>
+    <col min="12" max="12" width="13.875" style="3" customWidth="1"/>
+    <col min="13" max="17" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1129,84 +1182,196 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:22">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:25">
+      <c r="A4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:7">
       <c r="B5" s="3">
         <v>1001</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D5" s="3">
         <v>1001</v>
@@ -1214,16 +1379,16 @@
       <c r="E5" s="3">
         <v>1001</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:7">
       <c r="B6" s="3">
         <v>1002</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3">
         <v>1002</v>
@@ -1231,24 +1396,35 @@
       <c r="E6" s="3">
         <v>1002</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:2">
+    <row r="7" s="2" customFormat="1" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:8">
       <c r="B8" s="3">
         <v>1010</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3">
         <v>1010</v>
@@ -1256,16 +1432,19 @@
       <c r="E8" s="3">
         <v>1010</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1</v>
       </c>
+      <c r="H8" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:8">
       <c r="B9" s="3">
         <v>1011</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3">
         <v>1011</v>
@@ -1273,16 +1452,19 @@
       <c r="E9" s="3">
         <v>1011</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1</v>
       </c>
+      <c r="H9" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:8">
       <c r="B10" s="3">
         <v>1012</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3">
         <v>1012</v>
@@ -1290,16 +1472,19 @@
       <c r="E10" s="3">
         <v>1012</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1</v>
       </c>
+      <c r="H10" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:8">
       <c r="B11" s="3">
         <v>1013</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3">
         <v>1013</v>
@@ -1307,16 +1492,19 @@
       <c r="E11" s="3">
         <v>1013</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>1</v>
       </c>
+      <c r="H11" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:8">
       <c r="B12" s="3">
         <v>1014</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3">
         <v>1014</v>
@@ -1324,16 +1512,19 @@
       <c r="E12" s="3">
         <v>1014</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1</v>
       </c>
+      <c r="H12" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:8">
       <c r="B13" s="3">
         <v>1015</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D13" s="3">
         <v>1015</v>
@@ -1341,16 +1532,19 @@
       <c r="E13" s="3">
         <v>1015</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>1</v>
       </c>
+      <c r="H13" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:8">
       <c r="B14" s="3">
         <v>1016</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D14" s="3">
         <v>1016</v>
@@ -1358,11 +1552,17 @@
       <c r="E14" s="3">
         <v>1016</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="L1:P1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Luban/DataTables/Datas/Item.xlsx
+++ b/Luban/DataTables/Datas/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30705" windowHeight="9885"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -183,6 +183,24 @@
   </si>
   <si>
     <t>星2</t>
+  </si>
+  <si>
+    <t>礼包1</t>
+  </si>
+  <si>
+    <t>礼包2</t>
+  </si>
+  <si>
+    <t>礼包3</t>
+  </si>
+  <si>
+    <t>礼包4</t>
+  </si>
+  <si>
+    <t>礼包5</t>
+  </si>
+  <si>
+    <t>礼包6</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1168,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" style="3" customWidth="1"/>
@@ -1259,7 +1277,6 @@
       <c r="P2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
@@ -1311,7 +1328,6 @@
       <c r="P3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -1559,6 +1575,142 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="15" s="2" customFormat="1" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="3">
+        <v>10001</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10001</v>
+      </c>
+      <c r="E16" s="3">
+        <v>10001</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10002</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10002</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="3">
+        <v>10003</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3">
+        <v>10003</v>
+      </c>
+      <c r="E18" s="3">
+        <v>10003</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="3">
+        <v>10004</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10004</v>
+      </c>
+      <c r="E19" s="3">
+        <v>10004</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="3">
+        <v>10005</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="3">
+        <v>10005</v>
+      </c>
+      <c r="E20" s="3">
+        <v>10005</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="3">
+        <v>10006</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3">
+        <v>10006</v>
+      </c>
+      <c r="E21" s="3">
+        <v>10006</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L1:P1"/>
